--- a/src/app/store/product.xlsx
+++ b/src/app/store/product.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="167">
   <si>
     <t>id</t>
   </si>
@@ -31,328 +31,487 @@
     <t>price</t>
   </si>
   <si>
+    <t>rating</t>
+  </si>
+  <si>
     <t>active</t>
   </si>
   <si>
-    <t>French Fries</t>
-  </si>
-  <si>
-    <t>Crispy golden fries served with ketchup</t>
-  </si>
-  <si>
-    <t>International Snacks</t>
-  </si>
-  <si>
-    <t>/product/1.jpg</t>
+    <t>Chocolate Cake Slice</t>
+  </si>
+  <si>
+    <t>Rich chocolate cake slice topped with fresh strawberry and whipped cream</t>
+  </si>
+  <si>
+    <t>Cakes</t>
+  </si>
+  <si>
+    <t>/product/1.png</t>
   </si>
   <si>
     <t>true</t>
   </si>
   <si>
-    <t>Chicken Wings</t>
-  </si>
-  <si>
-    <t>Spicy grilled chicken wings (6 pcs)</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>/product/2.jpg</t>
-  </si>
-  <si>
-    <t>Mozzarella Sticks</t>
-  </si>
-  <si>
-    <t>Fried mozzarella sticks with marinara sauce</t>
-  </si>
-  <si>
-    <t>/product/3.jpg</t>
-  </si>
-  <si>
-    <t>Nachos</t>
-  </si>
-  <si>
-    <t>Tortilla chips with cheese jalapeños and salsa</t>
-  </si>
-  <si>
-    <t>/product/4.jpg</t>
-  </si>
-  <si>
-    <t>Onion Rings</t>
-  </si>
-  <si>
-    <t>Deep-fried battered onion rings</t>
-  </si>
-  <si>
-    <t>/product/5.jpg</t>
-  </si>
-  <si>
-    <t>Peanuts</t>
-  </si>
-  <si>
-    <t>Salted roasted peanuts</t>
-  </si>
-  <si>
-    <t>/product/6.jpg</t>
-  </si>
-  <si>
-    <t>Cheese Platter</t>
-  </si>
-  <si>
-    <t>Selection of cheeses with crackers</t>
-  </si>
-  <si>
-    <t>/product/7.jpg</t>
-  </si>
-  <si>
-    <t>Garlic Bread</t>
-  </si>
-  <si>
-    <t>Toasted bread with garlic butter</t>
-  </si>
-  <si>
-    <t>/product/8.jpg</t>
-  </si>
-  <si>
-    <t>Mini Burgers</t>
-  </si>
-  <si>
-    <t>Three mini beef sliders with cheese</t>
-  </si>
-  <si>
-    <t>/product/9.jpg</t>
-  </si>
-  <si>
-    <t>Hot Dog</t>
-  </si>
-  <si>
-    <t>Classic hot dog with mustard and ketchup</t>
-  </si>
-  <si>
-    <t>/product/10.jpg</t>
-  </si>
-  <si>
-    <t>Pastel de Nata</t>
-  </si>
-  <si>
-    <t>Traditional Portuguese custard tart</t>
-  </si>
-  <si>
-    <t>Portugal</t>
-  </si>
-  <si>
-    <t>/product/11.jpg</t>
-  </si>
-  <si>
-    <t>Bifana</t>
-  </si>
-  <si>
-    <t>Sliced pork sandwich with garlic and spices</t>
-  </si>
-  <si>
-    <t>/product/12.jpg</t>
-  </si>
-  <si>
-    <t>Prego Roll</t>
-  </si>
-  <si>
-    <t>Steak sandwich with garlic and mustard</t>
-  </si>
-  <si>
-    <t>/product/13.jpg</t>
-  </si>
-  <si>
-    <t>Caldo Verde</t>
-  </si>
-  <si>
-    <t>Cabbage and potato soup with chouriço</t>
-  </si>
-  <si>
-    <t>/product/14.jpg</t>
-  </si>
-  <si>
-    <t>Coxinha</t>
-  </si>
-  <si>
-    <t>Brazilian chicken croquette with dough</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>/product/15.jpg</t>
-  </si>
-  <si>
-    <t>Pão de Queijo</t>
-  </si>
-  <si>
-    <t>Cheese bread balls gluten free</t>
-  </si>
-  <si>
-    <t>/product/16.jpg</t>
-  </si>
-  <si>
-    <t>Kibe</t>
-  </si>
-  <si>
-    <t>Fried bulgur and beef croquette</t>
-  </si>
-  <si>
-    <t>/product/17.jpg</t>
-  </si>
-  <si>
-    <t>Brigadeiro</t>
-  </si>
-  <si>
-    <t>Chocolate fudge ball</t>
-  </si>
-  <si>
-    <t>/product/18.jpg</t>
-  </si>
-  <si>
-    <t>Patatas Bravas</t>
-  </si>
-  <si>
-    <t>Fried potatoes with spicy tomato sauce</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>/product/19.jpg</t>
-  </si>
-  <si>
-    <t>Tortilla Española</t>
-  </si>
-  <si>
-    <t>Spanish omelette with potatoes</t>
-  </si>
-  <si>
-    <t>/product/20.jpg</t>
-  </si>
-  <si>
-    <t>Croquetas</t>
-  </si>
-  <si>
-    <t>Creamy ham croquettes</t>
-  </si>
-  <si>
-    <t>/product/21.jpg</t>
-  </si>
-  <si>
-    <t>Pan con Tomate</t>
-  </si>
-  <si>
-    <t>Bread with tomato olive oil and garlic</t>
-  </si>
-  <si>
-    <t>/product/22.jpg</t>
-  </si>
-  <si>
-    <t>Croissant</t>
-  </si>
-  <si>
-    <t>Buttery flaky pastry</t>
+    <t>Margherita Pizza Slice</t>
+  </si>
+  <si>
+    <t>Classic pizza slice with feta, olives, and colorful bell peppers</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>/product/2.png</t>
+  </si>
+  <si>
+    <t>Cheese Pizza Slice</t>
+  </si>
+  <si>
+    <t>Cheesy pizza slice with a strawberry glaze topping</t>
+  </si>
+  <si>
+    <t>/product/3.png</t>
+  </si>
+  <si>
+    <t>Bread Loaf &amp; Cookies</t>
+  </si>
+  <si>
+    <t>Fresh-baked bread loaf served with homemade cookies</t>
   </si>
   <si>
     <t>Bakery</t>
   </si>
   <si>
-    <t>/product/23.jpg</t>
-  </si>
-  <si>
-    <t>Chocolate Croissant</t>
-  </si>
-  <si>
-    <t>Croissant filled with chocolate</t>
-  </si>
-  <si>
-    <t>/product/24.jpg</t>
-  </si>
-  <si>
-    <t>Muffin</t>
-  </si>
-  <si>
-    <t>Soft cake muffin with chocolate chips</t>
-  </si>
-  <si>
-    <t>/product/25.jpg</t>
-  </si>
-  <si>
-    <t>Cinnamon Roll</t>
-  </si>
-  <si>
-    <t>Sweet roll with cinnamon and icing</t>
-  </si>
-  <si>
-    <t>/product/26.jpg</t>
-  </si>
-  <si>
-    <t>Baguette Sandwich</t>
-  </si>
-  <si>
-    <t>Fresh baguette with ham and cheese</t>
-  </si>
-  <si>
-    <t>/product/27.jpg</t>
-  </si>
-  <si>
-    <t>Espresso</t>
-  </si>
-  <si>
-    <t>Strong black coffee shot</t>
-  </si>
-  <si>
-    <t>Coffee Shop</t>
-  </si>
-  <si>
-    <t>/product/28.jpg</t>
-  </si>
-  <si>
-    <t>Cappuccino</t>
-  </si>
-  <si>
-    <t>Espresso with steamed milk foam</t>
-  </si>
-  <si>
-    <t>/product/29.jpg</t>
-  </si>
-  <si>
-    <t>Latte</t>
-  </si>
-  <si>
-    <t>Espresso with hot milk</t>
-  </si>
-  <si>
-    <t>/product/30.jpg</t>
-  </si>
-  <si>
-    <t>Iced Coffee</t>
-  </si>
-  <si>
-    <t>Cold brewed coffee with ice</t>
-  </si>
-  <si>
-    <t>/product/31.jpg</t>
-  </si>
-  <si>
-    <t>Toast with Butter</t>
-  </si>
-  <si>
-    <t>Toasted bread with butter</t>
-  </si>
-  <si>
-    <t>/product/32.jpg</t>
-  </si>
-  <si>
-    <t>Toast with Jam</t>
-  </si>
-  <si>
-    <t>Toasted bread with fruit jam</t>
-  </si>
-  <si>
-    <t>/product/33.jpg</t>
+    <t>/product/4.png</t>
+  </si>
+  <si>
+    <t>Butter Croissant</t>
+  </si>
+  <si>
+    <t>Classic flaky butter croissant, golden and crispy</t>
+  </si>
+  <si>
+    <t>/product/5.png</t>
+  </si>
+  <si>
+    <t>Strawberry Pancake Stack</t>
+  </si>
+  <si>
+    <t>Fluffy pancakes topped with fresh strawberries and chocolate drizzle</t>
+  </si>
+  <si>
+    <t>Pancakes</t>
+  </si>
+  <si>
+    <t>/product/6.png</t>
+  </si>
+  <si>
+    <t>Chocolate Cherry Cake Slice</t>
+  </si>
+  <si>
+    <t>Decadent chocolate cake slice garnished with cherries</t>
+  </si>
+  <si>
+    <t>/product/7.png</t>
+  </si>
+  <si>
+    <t>Pepperoni Pizza Slice</t>
+  </si>
+  <si>
+    <t>Classic pizza slice loaded with pepperoni</t>
+  </si>
+  <si>
+    <t>/product/8.png</t>
+  </si>
+  <si>
+    <t>Classic Cheeseburger</t>
+  </si>
+  <si>
+    <t>Juicy beef patty with melted cheese, lettuce, and tomato</t>
+  </si>
+  <si>
+    <t>Burgers</t>
+  </si>
+  <si>
+    <t>/product/9.png</t>
+  </si>
+  <si>
+    <t>Classic Hamburger</t>
+  </si>
+  <si>
+    <t>All-American hamburger with fresh veggies and special sauce</t>
+  </si>
+  <si>
+    <t>/product/10.png</t>
+  </si>
+  <si>
+    <t>Waffle Stack with Butter</t>
+  </si>
+  <si>
+    <t>Stack of crispy waffles served with a generous pat of butter</t>
+  </si>
+  <si>
+    <t>Waffles</t>
+  </si>
+  <si>
+    <t>/product/11.png</t>
+  </si>
+  <si>
+    <t>Double Meat Burger</t>
+  </si>
+  <si>
+    <t>Double-patty burger stacked high with all the toppings</t>
+  </si>
+  <si>
+    <t>/product/12.png</t>
+  </si>
+  <si>
+    <t>Glazed Bread Loaf</t>
+  </si>
+  <si>
+    <t>Sweet glazed bread loaf, soft inside and golden outside</t>
+  </si>
+  <si>
+    <t>/product/13.png</t>
+  </si>
+  <si>
+    <t>Sliced Bread</t>
+  </si>
+  <si>
+    <t>Freshly sliced soft white bread loaf</t>
+  </si>
+  <si>
+    <t>/product/14.png</t>
+  </si>
+  <si>
+    <t>Cone Croissant</t>
+  </si>
+  <si>
+    <t>Unique cone-shaped croissant, perfect for fillings</t>
+  </si>
+  <si>
+    <t>/product/15.png</t>
+  </si>
+  <si>
+    <t>Strawberry Drizzle Cake Slice</t>
+  </si>
+  <si>
+    <t>Light cake slice with strawberry drizzle topping</t>
+  </si>
+  <si>
+    <t>/product/16.png</t>
+  </si>
+  <si>
+    <t>Croissant with Bagel Rings</t>
+  </si>
+  <si>
+    <t>Buttery croissant served alongside fresh bagel rings</t>
+  </si>
+  <si>
+    <t>/product/17.png</t>
+  </si>
+  <si>
+    <t>Dinner Rolls</t>
+  </si>
+  <si>
+    <t>Pair of soft, warm dinner rolls fresh from the oven</t>
+  </si>
+  <si>
+    <t>/product/18.png</t>
+  </si>
+  <si>
+    <t>French Fries with Truffle Dip</t>
+  </si>
+  <si>
+    <t>Crispy golden fries served with a chocolate truffle dip</t>
+  </si>
+  <si>
+    <t>Sides</t>
+  </si>
+  <si>
+    <t>/product/19.png</t>
+  </si>
+  <si>
+    <t>Chocolate Sandwich Stack</t>
+  </si>
+  <si>
+    <t>Indulgent chocolate-filled sandwich stack</t>
+  </si>
+  <si>
+    <t>Sandwiches</t>
+  </si>
+  <si>
+    <t>/product/20.png</t>
+  </si>
+  <si>
+    <t>Grilled Steak</t>
+  </si>
+  <si>
+    <t>Tender grilled steak, perfectly seasoned and cooked to perfection</t>
+  </si>
+  <si>
+    <t>Meat</t>
+  </si>
+  <si>
+    <t>/product/21.png</t>
+  </si>
+  <si>
+    <t>Croissant with Strawberries</t>
+  </si>
+  <si>
+    <t>Flaky croissant served with fresh ripe strawberries</t>
+  </si>
+  <si>
+    <t>/product/22.png</t>
+  </si>
+  <si>
+    <t>Almond Toast Sandwich</t>
+  </si>
+  <si>
+    <t>Toasted sandwich with almond spread and fillings</t>
+  </si>
+  <si>
+    <t>/product/23.png</t>
+  </si>
+  <si>
+    <t>Veggie Burger</t>
+  </si>
+  <si>
+    <t>Plant-based burger patty with fresh vegetables and greens</t>
+  </si>
+  <si>
+    <t>/product/24.png</t>
+  </si>
+  <si>
+    <t>Chocolate Raspberry Layer Cake</t>
+  </si>
+  <si>
+    <t>Decadent chocolate layer cake topped with fresh raspberries</t>
+  </si>
+  <si>
+    <t>/product/25.png</t>
+  </si>
+  <si>
+    <t>Veggie Pizza Slices</t>
+  </si>
+  <si>
+    <t>Pizza slices loaded with bell peppers, tomato, and vegetables</t>
+  </si>
+  <si>
+    <t>/product/26.png</t>
+  </si>
+  <si>
+    <t>Tomato Mozzarella Pizza Slice</t>
+  </si>
+  <si>
+    <t>Classic pizza slice with fresh tomato and melted mozzarella</t>
+  </si>
+  <si>
+    <t>/product/27.png</t>
+  </si>
+  <si>
+    <t>Butter Cookies</t>
+  </si>
+  <si>
+    <t>Crispy golden butter cookies, perfect with coffee or tea</t>
+  </si>
+  <si>
+    <t>/product/29.png</t>
+  </si>
+  <si>
+    <t>Chocolate Drizzled Croissants</t>
+  </si>
+  <si>
+    <t>Buttery croissants topped with rich chocolate drizzle</t>
+  </si>
+  <si>
+    <t>/product/30.png</t>
+  </si>
+  <si>
+    <t>Cheese Eclairs</t>
+  </si>
+  <si>
+    <t>Light pastry fingers filled with creamy cheese</t>
+  </si>
+  <si>
+    <t>/product/31.png</t>
+  </si>
+  <si>
+    <t>Sesame Seed Burger</t>
+  </si>
+  <si>
+    <t>Hearty burger with beef patty, cheese, and fresh veggies on sesame bun</t>
+  </si>
+  <si>
+    <t>/product/32.png</t>
+  </si>
+  <si>
+    <t>Plain Croissant</t>
+  </si>
+  <si>
+    <t>Simple classic croissant, lightly baked to golden perfection</t>
+  </si>
+  <si>
+    <t>/product/33.png</t>
+  </si>
+  <si>
+    <t>Cheeseburger Deluxe</t>
+  </si>
+  <si>
+    <t>Deluxe cheeseburger with layered cheese, tomato and lettuce</t>
+  </si>
+  <si>
+    <t>/product/34.png</t>
+  </si>
+  <si>
+    <t>Strawberry Layer Cake</t>
+  </si>
+  <si>
+    <t>Beautiful whole strawberry cake with cream layers and fresh fruit</t>
+  </si>
+  <si>
+    <t>/product/35.png</t>
+  </si>
+  <si>
+    <t>Caramel Chocolate Cake Slice</t>
+  </si>
+  <si>
+    <t>Rich chocolate cake slice drizzled with warm caramel sauce</t>
+  </si>
+  <si>
+    <t>/product/36.png</t>
+  </si>
+  <si>
+    <t>Butter Pancake Stack</t>
+  </si>
+  <si>
+    <t>Stack of fluffy pancakes with butter, syrup, and fresh strawberries</t>
+  </si>
+  <si>
+    <t>/product/37.png</t>
+  </si>
+  <si>
+    <t>Waffle &amp; Cookie Assortment</t>
+  </si>
+  <si>
+    <t>A mix of waffle bites, cookies, and sweet treats</t>
+  </si>
+  <si>
+    <t>Snacks</t>
+  </si>
+  <si>
+    <t>/product/38.png</t>
+  </si>
+  <si>
+    <t>Lasagna Slice</t>
+  </si>
+  <si>
+    <t>Hearty baked lasagna slice with rich meat and cheese layers</t>
+  </si>
+  <si>
+    <t>Savory</t>
+  </si>
+  <si>
+    <t>/product/39.png</t>
+  </si>
+  <si>
+    <t>Pizza Burger</t>
+  </si>
+  <si>
+    <t>Unique burger topped with pizza sauce, olives, and mozzarella</t>
+  </si>
+  <si>
+    <t>/product/40.png</t>
+  </si>
+  <si>
+    <t>Open-Faced Meat &amp; Egg Sandwich</t>
+  </si>
+  <si>
+    <t>Toasted open sandwich with meat patty, egg, and fresh vegetables</t>
+  </si>
+  <si>
+    <t>/product/41.png</t>
+  </si>
+  <si>
+    <t>Mille-Feuille Pastry</t>
+  </si>
+  <si>
+    <t>Delicate layered French pastry with cream filling</t>
+  </si>
+  <si>
+    <t>/product/42.png</t>
+  </si>
+  <si>
+    <t>Classic Butter Pancakes</t>
+  </si>
+  <si>
+    <t>Simple golden pancakes stacked with a generous knob of butter</t>
+  </si>
+  <si>
+    <t>/product/43.png</t>
+  </si>
+  <si>
+    <t>French Baguette</t>
+  </si>
+  <si>
+    <t>Authentic French baguette with a crispy crust and soft interior</t>
+  </si>
+  <si>
+    <t>/product/44.png</t>
+  </si>
+  <si>
+    <t>Sesame Seed Croissant</t>
+  </si>
+  <si>
+    <t>Flaky croissant topped with sesame seeds, baked to perfection</t>
+  </si>
+  <si>
+    <t>/product/45.png</t>
+  </si>
+  <si>
+    <t>Berry Pizza Cake Slice</t>
+  </si>
+  <si>
+    <t>Creative cake slice with pizza-style layers and berry topping</t>
+  </si>
+  <si>
+    <t>/product/46.png</t>
+  </si>
+  <si>
+    <t>Tomato Pizza Cake Slice</t>
+  </si>
+  <si>
+    <t>Savory-sweet pizza cake slice layered with tomato and cream</t>
+  </si>
+  <si>
+    <t>/product/47.png</t>
+  </si>
+  <si>
+    <t>Tomato Basil Cake Slice</t>
+  </si>
+  <si>
+    <t>Uniquely flavored slice with tomato, basil, and chocolate layers</t>
+  </si>
+  <si>
+    <t>/product/48.png</t>
+  </si>
+  <si>
+    <t>Hot Dog Sub Sandwich</t>
+  </si>
+  <si>
+    <t>Classic hot dog in a long sesame roll with toppings</t>
+  </si>
+  <si>
+    <t>/product/49.png</t>
+  </si>
+  <si>
+    <t>Crispy Flatbread Pancakes</t>
+  </si>
+  <si>
+    <t>Stack of flatbread with a golden pancake and butter</t>
+  </si>
+  <si>
+    <t>/product/50.png</t>
   </si>
 </sst>
 </file>
@@ -627,6 +786,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="2" max="2" width="23.13"/>
+    <col customWidth="1" min="3" max="3" width="25.25"/>
     <col customWidth="1" min="5" max="5" width="12.0"/>
   </cols>
   <sheetData>
@@ -652,28 +813,34 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>11</v>
+        <v>5.99</v>
+      </c>
+      <c r="G2" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -681,22 +848,25 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>11</v>
+        <v>3.99</v>
+      </c>
+      <c r="G3" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -704,22 +874,25 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>11</v>
+        <v>3.49</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -727,22 +900,25 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>6.99</v>
+      </c>
+      <c r="G5" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -750,22 +926,25 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2">
-        <v>3.8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>11</v>
+        <v>2.99</v>
+      </c>
+      <c r="G6" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -773,22 +952,25 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F7" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>11</v>
+        <v>7.99</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4.9</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -796,22 +978,25 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>11</v>
+        <v>5.49</v>
+      </c>
+      <c r="G8" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -819,22 +1004,25 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>11</v>
+        <v>4.29</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -842,22 +1030,25 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F10" s="2">
-        <v>6.8</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>11</v>
+        <v>8.99</v>
+      </c>
+      <c r="G10" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -865,22 +1056,25 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F11" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>11</v>
+        <v>7.99</v>
+      </c>
+      <c r="G11" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -888,22 +1082,25 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F12" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>11</v>
+        <v>6.99</v>
+      </c>
+      <c r="G12" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -911,22 +1108,25 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>11</v>
+        <v>11.99</v>
+      </c>
+      <c r="G13" s="2">
+        <v>4.9</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -934,22 +1134,25 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F14" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>11</v>
+        <v>5.49</v>
+      </c>
+      <c r="G14" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -957,22 +1160,25 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F15" s="2">
-        <v>3.8</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>11</v>
+        <v>3.99</v>
+      </c>
+      <c r="G15" s="2">
+        <v>4.4</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -980,22 +1186,25 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F16" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>11</v>
+        <v>3.49</v>
+      </c>
+      <c r="G16" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -1003,22 +1212,25 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F17" s="2">
-        <v>2.8</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>11</v>
+        <v>5.29</v>
+      </c>
+      <c r="G17" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -1026,22 +1238,25 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F18" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>11</v>
+        <v>4.99</v>
+      </c>
+      <c r="G18" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -1049,22 +1264,25 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F19" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>11</v>
+        <v>2.99</v>
+      </c>
+      <c r="G19" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -1072,22 +1290,25 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F20" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>11</v>
+        <v>4.99</v>
+      </c>
+      <c r="G20" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -1095,22 +1316,25 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F21" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>11</v>
+        <v>5.49</v>
+      </c>
+      <c r="G21" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -1118,22 +1342,25 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F22" s="2">
-        <v>4.2</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>11</v>
+        <v>18.99</v>
+      </c>
+      <c r="G22" s="2">
+        <v>4.9</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1141,22 +1368,25 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F23" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>11</v>
+        <v>4.49</v>
+      </c>
+      <c r="G23" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -1164,22 +1394,25 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F24" s="2">
-        <v>2.2</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>11</v>
+        <v>6.49</v>
+      </c>
+      <c r="G24" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -1187,22 +1420,25 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F25" s="2">
-        <v>2.8</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>11</v>
+        <v>8.49</v>
+      </c>
+      <c r="G25" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -1210,22 +1446,25 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F26" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>11</v>
+        <v>7.49</v>
+      </c>
+      <c r="G26" s="2">
+        <v>4.9</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -1233,22 +1472,25 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F27" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>11</v>
+        <v>5.49</v>
+      </c>
+      <c r="G27" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -1256,160 +1498,597 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F28" s="2">
-        <v>3.8</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>11</v>
+        <v>4.49</v>
+      </c>
+      <c r="G28" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F29" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>11</v>
+        <v>3.99</v>
+      </c>
+      <c r="G29" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F30" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>11</v>
+        <v>4.29</v>
+      </c>
+      <c r="G30" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F31" s="2">
-        <v>2.8</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>11</v>
+        <v>4.99</v>
+      </c>
+      <c r="G31" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F32" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>11</v>
+        <v>9.49</v>
+      </c>
+      <c r="G32" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F33" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>11</v>
+        <v>2.49</v>
+      </c>
+      <c r="G33" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F34" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>11</v>
+        <v>9.99</v>
+      </c>
+      <c r="G34" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="2">
+        <v>24.99</v>
+      </c>
+      <c r="G35" s="2">
+        <v>4.9</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" s="2">
+        <v>6.49</v>
+      </c>
+      <c r="G36" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>37.0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F37" s="2">
+        <v>7.49</v>
+      </c>
+      <c r="G37" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>38.0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" s="2">
+        <v>8.99</v>
+      </c>
+      <c r="G38" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>39.0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F39" s="2">
+        <v>10.99</v>
+      </c>
+      <c r="G39" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F40" s="2">
+        <v>10.49</v>
+      </c>
+      <c r="G40" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>41.0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F41" s="2">
+        <v>8.49</v>
+      </c>
+      <c r="G41" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F42" s="2">
+        <v>5.99</v>
+      </c>
+      <c r="G42" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>43.0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F43" s="2">
+        <v>6.49</v>
+      </c>
+      <c r="G43" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>44.0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F44" s="2">
+        <v>3.49</v>
+      </c>
+      <c r="G44" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F45" s="2">
+        <v>3.29</v>
+      </c>
+      <c r="G45" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>46.0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F46" s="2">
+        <v>5.99</v>
+      </c>
+      <c r="G46" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>47.0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F47" s="2">
+        <v>5.49</v>
+      </c>
+      <c r="G47" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>48.0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F48" s="2">
+        <v>5.29</v>
+      </c>
+      <c r="G48" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>49.0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F49" s="2">
+        <v>5.99</v>
+      </c>
+      <c r="G49" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F50" s="2">
+        <v>5.49</v>
+      </c>
+      <c r="G50" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
